--- a/survey_templates/034_family_dynamics_self_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/034_family_dynamics_self_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Conflict Frequency</t>
+          <t>Conflict Frequency Control</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Conflict Resolution</t>
+          <t>Conflict Resolution Control</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Conflict Control</t>
+          <t>Conflict Control Frequency</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1225,8 +1225,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'separated'}</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Separated'}</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'terrible'}</t>
+          <t>terrible</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Terrible'}</t>
+          <t>Terrible</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'grandparent'}</t>
+          <t>grandparent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Grandparent'}</t>
+          <t>Grandparent</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'discussion'}</t>
+          <t>discussion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Discussion'}</t>
+          <t>Discussion</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'avoidance'}</t>
+          <t>avoidance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Avoidance'}</t>
+          <t>Avoidance</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'aggression'}</t>
+          <t>aggression</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Aggression'}</t>
+          <t>Aggression</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'discussion'}</t>
+          <t>discussion</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Discussion'}</t>
+          <t>Discussion</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'avoidance'}</t>
+          <t>avoidance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Avoidance'}</t>
+          <t>Avoidance</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'aggression'}</t>
+          <t>aggression</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Aggression'}</t>
+          <t>Aggression</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2495,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
